--- a/data/trans_bre/P05A_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P05A_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,24</t>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-17,15%</t>
+          <t>-9,04%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 8,87</t>
+          <t>-0,97; 9,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 4,46</t>
+          <t>-5,76; 4,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 6,43</t>
+          <t>-4,7; 6,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 1,6</t>
+          <t>-3,48; 1,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 28,22</t>
+          <t>-2,81; 29,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 12,6</t>
+          <t>-13,99; 13,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 18,4</t>
+          <t>-11,46; 18,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-45,79; 30,44</t>
+          <t>-38,17; 35,06</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,5</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 11,12</t>
+          <t>2,23; 10,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 4,88</t>
+          <t>-4,02; 5,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,78</t>
+          <t>-4,29; 3,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 10,04</t>
+          <t>-0,49; 5,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 40,84</t>
+          <t>7,1; 39,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 16,71</t>
+          <t>-11,76; 16,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 13,23</t>
+          <t>-13,18; 12,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 175,5</t>
+          <t>-4,07; 53,97</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,07</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 4,23</t>
+          <t>-5,09; 4,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 6,9</t>
+          <t>-3,64; 6,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 5,51</t>
+          <t>-5,04; 5,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 49,62</t>
+          <t>-3,67; 5,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 16,8</t>
+          <t>-16,48; 16,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 18,8</t>
+          <t>-8,82; 18,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 15,49</t>
+          <t>-11,81; 15,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 292,33</t>
+          <t>-17,36; 29,56</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>2,67</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-0,74%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,36</t>
+          <t>3,54; 11,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 3,12</t>
+          <t>-6,04; 3,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 5,97</t>
+          <t>-2,72; 6,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 4,43</t>
+          <t>-1,45; 6,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 44,35</t>
+          <t>11,76; 45,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 6,61</t>
+          <t>-11,55; 7,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 16,65</t>
+          <t>-6,76; 17,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 14,4</t>
+          <t>-4,01; 22,46</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,39</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,11</t>
+          <t>2,5; 6,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,67</t>
+          <t>-2,15; 2,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,93</t>
+          <t>-1,76; 2,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 21,95</t>
+          <t>-0,28; 3,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,4; 25,16</t>
+          <t>8,29; 24,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 7,02</t>
+          <t>-5,26; 6,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 8,31</t>
+          <t>-4,78; 8,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 129,75</t>
+          <t>-1,47; 20,26</t>
         </is>
       </c>
     </row>
